--- a/config/generated/templates/BattleParticipantSlot.xlsx
+++ b/config/generated/templates/BattleParticipantSlot.xlsx
@@ -40,7 +40,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>33c37e3f3c9c7e2d</t>
+    <t>3921c64303047b69</t>
   </si>
   <si>
     <t>#name</t>
@@ -82,7 +82,7 @@
     <t>i32</t>
   </si>
   <si>
-    <t>ref&lt;Character.id&gt;</t>
+    <t>ref&lt;ContentIdentity.id&gt;</t>
   </si>
   <si>
     <t>string</t>
@@ -530,7 +530,7 @@
     <col min="2" max="2" width="21.7109375" style="5" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" style="5" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" style="5" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" style="5" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="22.7109375" style="5" customWidth="1"/>

--- a/config/generated/templates/BattleParticipantSlot.xlsx
+++ b/config/generated/templates/BattleParticipantSlot.xlsx
@@ -31,16 +31,16 @@
     <t>@key</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>3921c64303047b69</t>
+    <t>b1a585040dcdbb8d</t>
   </si>
   <si>
     <t>#name</t>
@@ -91,7 +91,7 @@
     <t>enum&lt;ParticipantSourceKind&gt;</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
